--- a/data/trans_orig/P40-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P40-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud autopercibida en los últimos 12 meses en 2007</t>
+          <t>Población según su salud autopercibida en los últimos 12 meses en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12392</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18719</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33787</t>
+          <t>33287</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58492</t>
+          <t>59137</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110244</t>
+          <t>109258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>153165</t>
+          <t>152678</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150732</t>
+          <t>151609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200741</t>
+          <t>202930</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>249767</t>
+          <t>249738</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>303124</t>
+          <t>304793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>444756</t>
+          <t>446754</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>514905</t>
+          <t>516576</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>708216</t>
+          <t>709381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>803893</t>
+          <t>802802</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>555345</t>
+          <t>554905</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>617552</t>
+          <t>618697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>568421</t>
+          <t>565758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>642025</t>
+          <t>637982</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1143295</t>
+          <t>1141557</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1241553</t>
+          <t>1234715</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,67%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99879</t>
+          <t>100036</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>141167</t>
+          <t>138266</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78245</t>
+          <t>80687</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118267</t>
+          <t>115521</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185503</t>
+          <t>187137</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>244166</t>
+          <t>243144</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19222</t>
+          <t>19278</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>21397</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21304</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25906</t>
+          <t>26221</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49371</t>
+          <t>50453</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36699</t>
+          <t>37186</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63878</t>
+          <t>64321</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>112747</t>
+          <t>112332</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>157550</t>
+          <t>157286</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>208895</t>
+          <t>206090</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>263816</t>
+          <t>263770</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332067</t>
+          <t>331596</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>407079</t>
+          <t>404696</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1123453</t>
+          <t>1122249</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1198175</t>
+          <t>1202776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>999229</t>
+          <t>1000207</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1075349</t>
+          <t>1077574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2139871</t>
+          <t>2144466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2251365</t>
+          <t>2255416</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>348537</t>
+          <t>343331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>420412</t>
+          <t>414409</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>242147</t>
+          <t>240192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>300392</t>
+          <t>299395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>604452</t>
+          <t>603100</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>701954</t>
+          <t>695978</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21299</t>
+          <t>20322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>11948</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31036</t>
+          <t>30698</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26696</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51606</t>
+          <t>50812</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41835</t>
+          <t>43442</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70850</t>
+          <t>71214</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76344</t>
+          <t>75887</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>114856</t>
+          <t>113381</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>332782</t>
+          <t>330882</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>381073</t>
+          <t>378172</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>276006</t>
+          <t>274534</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>319015</t>
+          <t>318370</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>616756</t>
+          <t>624290</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>682519</t>
+          <t>687589</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,9%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>124924</t>
+          <t>127743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167697</t>
+          <t>170575</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92723</t>
+          <t>92462</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>130286</t>
+          <t>130651</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>230281</t>
+          <t>230912</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>287872</t>
+          <t>286021</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>14841</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30470</t>
+          <t>31298</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39702</t>
+          <t>38536</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54687</t>
+          <t>55172</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>86899</t>
+          <t>87185</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>149609</t>
+          <t>150267</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>199997</t>
+          <t>201652</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>214592</t>
+          <t>213008</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>275655</t>
+          <t>276857</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>410043</t>
+          <t>408310</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>488261</t>
+          <t>486530</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>719001</t>
+          <t>719836</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>814961</t>
+          <t>818788</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1149963</t>
+          <t>1158393</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1275227</t>
+          <t>1276432</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2054545</t>
+          <t>2048100</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2159451</t>
+          <t>2157650</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1877108</t>
+          <t>1876910</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2001753</t>
+          <t>1993177</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3973038</t>
+          <t>3967181</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4126198</t>
+          <t>4121434</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,97%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>600371</t>
+          <t>600617</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>689622</t>
+          <t>698092</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>436528</t>
+          <t>438108</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>521404</t>
+          <t>520091</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1061569</t>
+          <t>1066689</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1181446</t>
+          <t>1187120</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud autopercibida en los últimos 12 meses en 2012</t>
+          <t>Población según su salud autopercibida en los últimos 12 meses en 2012 (tasa de respuesta: 98,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13696</t>
+          <t>14052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>13638</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32790</t>
+          <t>33342</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>19663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42174</t>
+          <t>42401</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42880</t>
+          <t>42467</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73581</t>
+          <t>74010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98857</t>
+          <t>95468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139192</t>
+          <t>140849</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149334</t>
+          <t>149176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200938</t>
+          <t>200283</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>237006</t>
+          <t>233980</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>294209</t>
+          <t>295240</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>457181</t>
+          <t>457841</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>529487</t>
+          <t>529035</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>709771</t>
+          <t>712848</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>805159</t>
+          <t>802273</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>511066</t>
+          <t>512755</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>575147</t>
+          <t>577888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>588931</t>
+          <t>589121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>666955</t>
+          <t>662985</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1123575</t>
+          <t>1119917</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1221522</t>
+          <t>1219021</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,99%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75167</t>
+          <t>76118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115177</t>
+          <t>113104</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60043</t>
+          <t>59199</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94824</t>
+          <t>93504</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142002</t>
+          <t>144176</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>193036</t>
+          <t>196292</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>9193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12490</t>
+          <t>12241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15656</t>
+          <t>15941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>27251</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27312</t>
+          <t>27270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52631</t>
+          <t>53646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42529</t>
+          <t>42042</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72995</t>
+          <t>73001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>158104</t>
+          <t>159092</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>212766</t>
+          <t>213115</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>205460</t>
+          <t>205887</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>262658</t>
+          <t>264062</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>379000</t>
+          <t>380054</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>455416</t>
+          <t>465239</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1211543</t>
+          <t>1212897</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1297859</t>
+          <t>1302584</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1126752</t>
+          <t>1126559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1210340</t>
+          <t>1206332</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2357170</t>
+          <t>2368297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2478656</t>
+          <t>2480518</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,56%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>436679</t>
+          <t>430467</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>510282</t>
+          <t>512242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264228</t>
+          <t>265279</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>326633</t>
+          <t>327436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>721587</t>
+          <t>718453</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>826567</t>
+          <t>818001</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -5056,97 +5056,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2121</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>15557</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>16727</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25131</t>
+          <t>26786</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22591</t>
+          <t>23080</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48388</t>
+          <t>48429</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21542</t>
+          <t>22267</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46144</t>
+          <t>46788</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51057</t>
+          <t>48561</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84620</t>
+          <t>83609</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>258905</t>
+          <t>258843</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>307137</t>
+          <t>304016</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>309005</t>
+          <t>307147</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>348470</t>
+          <t>348181</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>581850</t>
+          <t>579777</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>642114</t>
+          <t>645511</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134607</t>
+          <t>136604</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>179118</t>
+          <t>180916</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68324</t>
+          <t>69622</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104210</t>
+          <t>105300</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>214884</t>
+          <t>214896</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>273022</t>
+          <t>273572</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15897</t>
+          <t>16807</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>18502</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39734</t>
+          <t>40638</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>26673</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>51292</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62270</t>
+          <t>60950</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99643</t>
+          <t>99326</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>138489</t>
+          <t>140345</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188330</t>
+          <t>190104</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>213836</t>
+          <t>213242</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>273580</t>
+          <t>273937</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>439901</t>
+          <t>442161</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>525453</t>
+          <t>530678</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>713521</t>
+          <t>710099</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>812974</t>
+          <t>809554</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1160983</t>
+          <t>1180574</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1301074</t>
+          <t>1307226</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2028194</t>
+          <t>2022707</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2138181</t>
+          <t>2141311</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2060637</t>
+          <t>2054532</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2178193</t>
+          <t>2183542</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4129432</t>
+          <t>4128629</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4290217</t>
+          <t>4288737</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>675107</t>
+          <t>673699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>771541</t>
+          <t>775893</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>418594</t>
+          <t>416118</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>499460</t>
+          <t>498706</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1121507</t>
+          <t>1114377</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1253196</t>
+          <t>1246054</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud autopercibida en los últimos 12 meses en 2016</t>
+          <t>Población según su salud autopercibida en los últimos 12 meses en 2016 (tasa de respuesta: 99,22%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23430</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27829</t>
+          <t>28136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28564</t>
+          <t>29272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51879</t>
+          <t>53902</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69794</t>
+          <t>70142</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106562</t>
+          <t>109416</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105339</t>
+          <t>105826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152022</t>
+          <t>150394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175943</t>
+          <t>181494</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>226295</t>
+          <t>230256</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>342829</t>
+          <t>341881</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>405549</t>
+          <t>411236</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>537208</t>
+          <t>536326</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>616341</t>
+          <t>617300</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>381698</t>
+          <t>380730</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>435712</t>
+          <t>431940</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>406427</t>
+          <t>404591</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>471708</t>
+          <t>471031</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>802317</t>
+          <t>801253</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>887134</t>
+          <t>888965</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,25%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75795</t>
+          <t>75759</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111584</t>
+          <t>112189</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59951</t>
+          <t>60965</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92851</t>
+          <t>94614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144061</t>
+          <t>145136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>195532</t>
+          <t>196407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>13481</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15032</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21398</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18882</t>
+          <t>18459</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40041</t>
+          <t>40570</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42244</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73175</t>
+          <t>73730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67243</t>
+          <t>66263</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104873</t>
+          <t>104936</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>186896</t>
+          <t>187308</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>241154</t>
+          <t>244441</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>254909</t>
+          <t>257828</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>322054</t>
+          <t>322514</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>459723</t>
+          <t>459663</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>546483</t>
+          <t>551467</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1191438</t>
+          <t>1189627</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1281484</t>
+          <t>1280682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1134980</t>
+          <t>1133262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1228915</t>
+          <t>1225948</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2359773</t>
+          <t>2356489</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2485597</t>
+          <t>2482833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,51%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>546331</t>
+          <t>543984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>626266</t>
+          <t>626359</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>398738</t>
+          <t>397370</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>474412</t>
+          <t>472689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>959522</t>
+          <t>971783</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1074811</t>
+          <t>1078810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14170</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15829</t>
+          <t>16113</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23320</t>
+          <t>25029</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26261</t>
+          <t>26874</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52977</t>
+          <t>53794</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34810</t>
+          <t>35145</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62298</t>
+          <t>63015</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68587</t>
+          <t>68911</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105051</t>
+          <t>104244</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>304803</t>
+          <t>303766</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>350044</t>
+          <t>349269</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>322110</t>
+          <t>322688</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>368126</t>
+          <t>366141</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>636882</t>
+          <t>635064</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>703509</t>
+          <t>701511</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,46%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>150866</t>
+          <t>151820</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196599</t>
+          <t>194683</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>121147</t>
+          <t>123251</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>161064</t>
+          <t>163152</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>285821</t>
+          <t>287974</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>346087</t>
+          <t>348460</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>18900</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33775</t>
+          <t>35060</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21355</t>
+          <t>21333</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46159</t>
+          <t>44685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58382</t>
+          <t>58067</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92236</t>
+          <t>92987</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127818</t>
+          <t>124998</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>179793</t>
+          <t>175661</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>197774</t>
+          <t>195871</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>258024</t>
+          <t>258562</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>414962</t>
+          <t>415351</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>494321</t>
+          <t>497267</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>660110</t>
+          <t>659087</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>763254</t>
+          <t>763323</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1101517</t>
+          <t>1102471</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1229507</t>
+          <t>1228011</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1909736</t>
+          <t>1911124</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2023429</t>
+          <t>2032637</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1906259</t>
+          <t>1907358</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2027606</t>
+          <t>2027638</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3841063</t>
+          <t>3850991</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4018529</t>
+          <t>4015470</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,54%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>802464</t>
+          <t>800148</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>900918</t>
+          <t>903957</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>606426</t>
+          <t>606412</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>695685</t>
+          <t>700562</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1433630</t>
+          <t>1434387</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1571641</t>
+          <t>1571468</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud autopercibida en los últimos 12 meses en 2023</t>
+          <t>Población según su salud autopercibida en los últimos 12 meses en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26507</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22921</t>
+          <t>22990</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>39302</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37332</t>
+          <t>38059</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59510</t>
+          <t>58844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45284</t>
+          <t>45971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68641</t>
+          <t>69411</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105123</t>
+          <t>104472</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132768</t>
+          <t>132557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155386</t>
+          <t>154957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>193239</t>
+          <t>192522</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>122372</t>
+          <t>120969</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>156743</t>
+          <t>157124</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>262719</t>
+          <t>260810</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>304724</t>
+          <t>302613</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>392794</t>
+          <t>394477</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>447359</t>
+          <t>450220</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>238851</t>
+          <t>237594</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>279146</t>
+          <t>280701</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>281964</t>
+          <t>280110</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>322076</t>
+          <t>321569</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>531224</t>
+          <t>532198</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>594825</t>
+          <t>591885</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,59%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30976</t>
+          <t>31439</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60825</t>
+          <t>62322</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>15965</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32948</t>
+          <t>32953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53517</t>
+          <t>52134</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87326</t>
+          <t>85973</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27472</t>
+          <t>26971</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,82 +10307,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>11345</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6936</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18011</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>27930</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>18556</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>39703</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11345</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6899</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>19921</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>27930</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>19341</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>39010</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27082</t>
+          <t>28284</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56926</t>
+          <t>56838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40588</t>
+          <t>41735</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72037</t>
+          <t>72547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76549</t>
+          <t>77522</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>119841</t>
+          <t>120020</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>188155</t>
+          <t>187933</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314944</t>
+          <t>315879</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>310541</t>
+          <t>315237</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>591399</t>
+          <t>598992</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>559011</t>
+          <t>559949</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>878245</t>
+          <t>875552</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1465837</t>
+          <t>1467104</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1794535</t>
+          <t>1803660</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1358168</t>
+          <t>1359374</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1705386</t>
+          <t>1684068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2880952</t>
+          <t>2876224</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3363623</t>
+          <t>3345394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>269805</t>
+          <t>267248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>463584</t>
+          <t>460483</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193143</t>
+          <t>197225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>356078</t>
+          <t>346401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>525866</t>
+          <t>537491</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>765226</t>
+          <t>761981</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18292</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13050</t>
+          <t>12826</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26236</t>
+          <t>27184</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54188</t>
+          <t>53466</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85705</t>
+          <t>84835</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66474</t>
+          <t>66529</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95355</t>
+          <t>95014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>126533</t>
+          <t>128697</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>173323</t>
+          <t>170811</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>364645</t>
+          <t>364601</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>422683</t>
+          <t>422572</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>438806</t>
+          <t>436535</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>481450</t>
+          <t>479831</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>815789</t>
+          <t>815996</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>890603</t>
+          <t>889753</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,07%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>143947</t>
+          <t>146222</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>201436</t>
+          <t>203776</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>93107</t>
+          <t>92296</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128440</t>
+          <t>129789</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>250139</t>
+          <t>245416</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>320008</t>
+          <t>316530</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24772</t>
+          <t>24279</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50424</t>
+          <t>49099</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33540</t>
+          <t>33431</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55978</t>
+          <t>55901</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65075</t>
+          <t>64028</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98527</t>
+          <t>97215</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>81431</t>
+          <t>81297</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>128812</t>
+          <t>128738</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>146724</t>
+          <t>149687</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>205239</t>
+          <t>207959</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>250834</t>
+          <t>249435</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>326736</t>
+          <t>323681</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>367982</t>
+          <t>370117</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>530468</t>
+          <t>529520</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>654169</t>
+          <t>660271</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>943948</t>
+          <t>933177</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1112463</t>
+          <t>1089913</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1468402</t>
+          <t>1415049</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2108084</t>
+          <t>2109282</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2490702</t>
+          <t>2485108</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2119477</t>
+          <t>2115729</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2506949</t>
+          <t>2514394</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4271970</t>
+          <t>4276852</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4811529</t>
+          <t>4811774</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,72%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>476742</t>
+          <t>472968</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>684156</t>
+          <t>685086</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>331165</t>
+          <t>320520</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>497101</t>
+          <t>490315</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>864596</t>
+          <t>865987</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1125186</t>
+          <t>1123129</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P40-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P40-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>19290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33287</t>
+          <t>33542</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59137</t>
+          <t>56942</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109258</t>
+          <t>110255</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152678</t>
+          <t>153649</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151609</t>
+          <t>149730</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>202930</t>
+          <t>200357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>249738</t>
+          <t>247730</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>304793</t>
+          <t>306175</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446754</t>
+          <t>444687</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>516576</t>
+          <t>517994</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>709381</t>
+          <t>710476</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>802802</t>
+          <t>801068</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>554905</t>
+          <t>555014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>618697</t>
+          <t>618993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>565758</t>
+          <t>561821</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>637982</t>
+          <t>635445</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1141557</t>
+          <t>1146077</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1234715</t>
+          <t>1240486</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,92%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100036</t>
+          <t>98996</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>138266</t>
+          <t>140439</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80687</t>
+          <t>79097</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>115521</t>
+          <t>117857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>187137</t>
+          <t>188953</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>243144</t>
+          <t>245825</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21397</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>21284</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26221</t>
+          <t>25644</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50453</t>
+          <t>48720</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37186</t>
+          <t>37660</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64321</t>
+          <t>65502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>112332</t>
+          <t>111435</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>157286</t>
+          <t>158383</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>206090</t>
+          <t>206043</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>263770</t>
+          <t>260535</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>331596</t>
+          <t>332173</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>404696</t>
+          <t>407476</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1122249</t>
+          <t>1122372</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1202776</t>
+          <t>1199829</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1000207</t>
+          <t>1003342</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1077574</t>
+          <t>1074107</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2144466</t>
+          <t>2143683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2255416</t>
+          <t>2256426</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,81%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343331</t>
+          <t>349969</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>414409</t>
+          <t>420801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>240192</t>
+          <t>239559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>299395</t>
+          <t>299995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>603100</t>
+          <t>604826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>695978</t>
+          <t>696029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>10894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20322</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15699</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30698</t>
+          <t>30342</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>26191</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50812</t>
+          <t>50555</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43442</t>
+          <t>42685</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71214</t>
+          <t>72250</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75887</t>
+          <t>74890</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>113381</t>
+          <t>112206</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>330882</t>
+          <t>333422</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>378172</t>
+          <t>380491</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>274534</t>
+          <t>275421</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>318370</t>
+          <t>317861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>624290</t>
+          <t>623718</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>687589</t>
+          <t>684107</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>127743</t>
+          <t>125175</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>170575</t>
+          <t>168647</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92462</t>
+          <t>92361</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>130651</t>
+          <t>130104</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>230912</t>
+          <t>229014</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>286021</t>
+          <t>285607</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12274</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>31282</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38536</t>
+          <t>38689</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>55172</t>
+          <t>55387</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>87185</t>
+          <t>86736</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>150267</t>
+          <t>151658</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>201652</t>
+          <t>202130</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>213008</t>
+          <t>215023</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>276857</t>
+          <t>273709</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>408310</t>
+          <t>408113</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>486530</t>
+          <t>487196</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>719836</t>
+          <t>718112</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>818788</t>
+          <t>820301</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1158393</t>
+          <t>1149989</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1276432</t>
+          <t>1280183</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2048100</t>
+          <t>2052187</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2157650</t>
+          <t>2159173</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1876910</t>
+          <t>1885894</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1993177</t>
+          <t>1996888</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3967181</t>
+          <t>3960798</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4121434</t>
+          <t>4122734</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,99%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>600617</t>
+          <t>603049</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>698092</t>
+          <t>692888</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>438108</t>
+          <t>437534</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>520091</t>
+          <t>520380</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1066689</t>
+          <t>1060892</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1187120</t>
+          <t>1187191</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14052</t>
+          <t>13710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>13328</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33342</t>
+          <t>33207</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19663</t>
+          <t>18644</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42401</t>
+          <t>41377</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42467</t>
+          <t>40440</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74010</t>
+          <t>71575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95468</t>
+          <t>97076</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140849</t>
+          <t>136562</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149176</t>
+          <t>145934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200283</t>
+          <t>199772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>233980</t>
+          <t>235858</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>295240</t>
+          <t>293708</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>457841</t>
+          <t>456844</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>529035</t>
+          <t>532304</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>712848</t>
+          <t>713416</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>802273</t>
+          <t>805441</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>512755</t>
+          <t>514160</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>577888</t>
+          <t>576680</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>589121</t>
+          <t>589688</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>662985</t>
+          <t>668380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1119917</t>
+          <t>1122645</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1219021</t>
+          <t>1223003</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,16%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76118</t>
+          <t>77405</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>113104</t>
+          <t>114682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59199</t>
+          <t>60414</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93504</t>
+          <t>93887</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144176</t>
+          <t>144079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>196292</t>
+          <t>193996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>18672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27251</t>
+          <t>26898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27270</t>
+          <t>27429</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53646</t>
+          <t>53990</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>41741</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>73468</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>159092</t>
+          <t>158306</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>213115</t>
+          <t>213036</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>205887</t>
+          <t>206518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>264062</t>
+          <t>261418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>380054</t>
+          <t>380490</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>465239</t>
+          <t>458201</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1212897</t>
+          <t>1213001</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1302584</t>
+          <t>1297080</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1126559</t>
+          <t>1125904</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1206332</t>
+          <t>1203430</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2368297</t>
+          <t>2365963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2480518</t>
+          <t>2481201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,58%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>430467</t>
+          <t>435498</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>512242</t>
+          <t>514898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>265279</t>
+          <t>268408</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>327436</t>
+          <t>330535</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>718453</t>
+          <t>719215</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>818001</t>
+          <t>822329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15557</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48429</t>
+          <t>47969</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22267</t>
+          <t>21940</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46788</t>
+          <t>45616</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48561</t>
+          <t>50263</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83609</t>
+          <t>85117</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>258843</t>
+          <t>257837</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>304016</t>
+          <t>303961</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>307147</t>
+          <t>308040</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>348181</t>
+          <t>350163</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>579777</t>
+          <t>581812</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>645511</t>
+          <t>645720</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,1%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>136604</t>
+          <t>138391</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>180916</t>
+          <t>183313</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69622</t>
+          <t>69143</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105300</t>
+          <t>105979</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>214896</t>
+          <t>215979</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>273572</t>
+          <t>272533</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16807</t>
+          <t>16909</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18502</t>
+          <t>18539</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40638</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26673</t>
+          <t>27009</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51292</t>
+          <t>50685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60950</t>
+          <t>61461</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99326</t>
+          <t>97732</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>140345</t>
+          <t>141012</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>190104</t>
+          <t>191535</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>213242</t>
+          <t>210307</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>273937</t>
+          <t>273858</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>442161</t>
+          <t>439409</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>530678</t>
+          <t>524477</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>710099</t>
+          <t>714942</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>809554</t>
+          <t>812179</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1180574</t>
+          <t>1176380</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1307226</t>
+          <t>1310741</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2022707</t>
+          <t>2022800</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2141311</t>
+          <t>2145215</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2054532</t>
+          <t>2066400</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2183542</t>
+          <t>2182142</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4128629</t>
+          <t>4124882</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4288737</t>
+          <t>4296074</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,2%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>673699</t>
+          <t>673387</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775893</t>
+          <t>776676</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>416118</t>
+          <t>415119</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>498706</t>
+          <t>496303</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1114377</t>
+          <t>1117109</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1246054</t>
+          <t>1242791</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24081</t>
+          <t>24515</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28136</t>
+          <t>28847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29272</t>
+          <t>29046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53902</t>
+          <t>52536</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70142</t>
+          <t>69562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109416</t>
+          <t>106859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105826</t>
+          <t>104068</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150394</t>
+          <t>148626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>181494</t>
+          <t>180438</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>230256</t>
+          <t>227684</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>341881</t>
+          <t>343135</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>411236</t>
+          <t>406676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>536326</t>
+          <t>536875</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>617300</t>
+          <t>615957</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>380730</t>
+          <t>381413</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>431940</t>
+          <t>432507</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>404591</t>
+          <t>404987</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>471031</t>
+          <t>471776</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>801253</t>
+          <t>805664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>888965</t>
+          <t>887983</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,19%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75759</t>
+          <t>76536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>112189</t>
+          <t>110546</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60965</t>
+          <t>60652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94614</t>
+          <t>97409</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145136</t>
+          <t>145405</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>196407</t>
+          <t>195716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13746</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21792</t>
+          <t>19981</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40570</t>
+          <t>39775</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42105</t>
+          <t>42810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73730</t>
+          <t>75027</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66263</t>
+          <t>67023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104936</t>
+          <t>104604</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>187308</t>
+          <t>186551</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>244441</t>
+          <t>244748</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>257828</t>
+          <t>255159</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>322514</t>
+          <t>319976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>459663</t>
+          <t>463228</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>551467</t>
+          <t>548251</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1189627</t>
+          <t>1193210</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1280682</t>
+          <t>1278149</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1133262</t>
+          <t>1141201</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1225948</t>
+          <t>1227460</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2356489</t>
+          <t>2354961</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2482833</t>
+          <t>2480036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,44%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>543984</t>
+          <t>541789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>626359</t>
+          <t>626544</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>397370</t>
+          <t>399798</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>472689</t>
+          <t>470202</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>971783</t>
+          <t>958429</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1078810</t>
+          <t>1070463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14016</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16113</t>
+          <t>14847</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25029</t>
+          <t>24267</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26874</t>
+          <t>25931</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53794</t>
+          <t>51963</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35145</t>
+          <t>34853</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63015</t>
+          <t>63398</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68911</t>
+          <t>67981</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>104244</t>
+          <t>107037</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>303766</t>
+          <t>303635</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>349269</t>
+          <t>349829</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>322688</t>
+          <t>321155</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>366141</t>
+          <t>368411</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>635064</t>
+          <t>638629</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>701511</t>
+          <t>704735</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,76%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151820</t>
+          <t>150665</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>194683</t>
+          <t>195073</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>123251</t>
+          <t>122905</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>163152</t>
+          <t>165511</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>287974</t>
+          <t>283844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>348460</t>
+          <t>345843</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18900</t>
+          <t>18820</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35060</t>
+          <t>32942</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>21471</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44685</t>
+          <t>45738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58067</t>
+          <t>58558</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92987</t>
+          <t>93208</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>124998</t>
+          <t>125299</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>175661</t>
+          <t>176158</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>195871</t>
+          <t>196183</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>258562</t>
+          <t>256969</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>415351</t>
+          <t>415418</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>497267</t>
+          <t>497716</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>659087</t>
+          <t>658294</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>763323</t>
+          <t>758580</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1102471</t>
+          <t>1088910</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1228011</t>
+          <t>1228131</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1911124</t>
+          <t>1911867</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2032637</t>
+          <t>2028907</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1907358</t>
+          <t>1912731</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2027638</t>
+          <t>2034419</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3850991</t>
+          <t>3853388</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4015470</t>
+          <t>4023427</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,66%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>800148</t>
+          <t>799759</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>903957</t>
+          <t>900890</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>606412</t>
+          <t>607063</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>700562</t>
+          <t>696296</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1434387</t>
+          <t>1435675</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1571468</t>
+          <t>1567114</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17561</t>
+          <t>18888</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26020</t>
+          <t>29028</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29931</t>
+          <t>33367</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22990</t>
+          <t>25491</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39302</t>
+          <t>42596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>47493</t>
+          <t>52255</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38059</t>
+          <t>42363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58844</t>
+          <t>65835</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55964</t>
+          <t>59164</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45971</t>
+          <t>47513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69411</t>
+          <t>72996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,17 +9753,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>117900</t>
+          <t>128285</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104472</t>
+          <t>112572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132557</t>
+          <t>143873</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>173864</t>
+          <t>187449</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154957</t>
+          <t>169436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>192522</t>
+          <t>208863</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>137764</t>
+          <t>147739</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120969</t>
+          <t>130039</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>157124</t>
+          <t>167161</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>282315</t>
+          <t>302174</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>260810</t>
+          <t>280582</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>302613</t>
+          <t>323490</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>420079</t>
+          <t>449912</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>394477</t>
+          <t>421645</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>450220</t>
+          <t>479603</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>259556</t>
+          <t>292830</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>237594</t>
+          <t>271312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>280701</t>
+          <t>316886</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>301865</t>
+          <t>333275</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>280110</t>
+          <t>311692</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>321569</t>
+          <t>357240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>561421</t>
+          <t>626105</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>532198</t>
+          <t>593767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>591885</t>
+          <t>658207</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>47,0%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>44093</t>
+          <t>59908</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31439</t>
+          <t>43044</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62322</t>
+          <t>79819</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23497</t>
+          <t>24937</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15965</t>
+          <t>17631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32953</t>
+          <t>35516</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>67590</t>
+          <t>84845</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52134</t>
+          <t>67148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85973</t>
+          <t>107441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16585</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>9677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26971</t>
+          <t>27133</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27930</t>
+          <t>30170</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>20698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39703</t>
+          <t>40467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41869</t>
+          <t>44230</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28284</t>
+          <t>33115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56838</t>
+          <t>58950</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57233</t>
+          <t>62157</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41735</t>
+          <t>50109</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72547</t>
+          <t>74163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>99102</t>
+          <t>106387</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77522</t>
+          <t>90596</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120020</t>
+          <t>124366</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>268957</t>
+          <t>284305</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>187933</t>
+          <t>253636</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315879</t>
+          <t>316738</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>411871</t>
+          <t>382383</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>315237</t>
+          <t>350768</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>598992</t>
+          <t>414945</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>680828</t>
+          <t>666688</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>559949</t>
+          <t>625220</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>875552</t>
+          <t>713039</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1572188</t>
+          <t>1474470</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1467104</t>
+          <t>1423535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1803660</t>
+          <t>1528716</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1496491</t>
+          <t>1439111</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1359374</t>
+          <t>1396037</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1684068</t>
+          <t>1483075</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3068679</t>
+          <t>2913581</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2876224</t>
+          <t>2847323</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3345394</t>
+          <t>2981310</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>390728</t>
+          <t>410125</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>267248</t>
+          <t>366665</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>460483</t>
+          <t>463645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>260882</t>
+          <t>275007</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>197225</t>
+          <t>243928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>346401</t>
+          <t>309698</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>651610</t>
+          <t>685132</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>537491</t>
+          <t>623160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>761981</t>
+          <t>744961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,22 +11039,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>11008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18189</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12826</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,22 +11152,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>18103</t>
+          <t>20431</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11885</t>
+          <t>13186</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27184</t>
+          <t>30105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67817</t>
+          <t>72354</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53466</t>
+          <t>57033</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84835</t>
+          <t>89831</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>80305</t>
+          <t>92821</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66529</t>
+          <t>78462</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95014</t>
+          <t>111220</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>148122</t>
+          <t>165175</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>128697</t>
+          <t>142821</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>170811</t>
+          <t>187817</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>395109</t>
+          <t>444786</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>364601</t>
+          <t>418567</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>422572</t>
+          <t>475310</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>460015</t>
+          <t>510995</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>436535</t>
+          <t>487786</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>479831</t>
+          <t>533756</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>855124</t>
+          <t>955781</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>815996</t>
+          <t>917162</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>889753</t>
+          <t>993457</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,68%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>170950</t>
+          <t>180036</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146222</t>
+          <t>154508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203776</t>
+          <t>207607</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>110051</t>
+          <t>119552</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92296</t>
+          <t>101199</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>129789</t>
+          <t>139307</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>281001</t>
+          <t>299587</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>245416</t>
+          <t>265746</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>316530</t>
+          <t>332357</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,67 +11651,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24279</t>
+          <t>27572</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49099</t>
+          <t>53033</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>49388</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>39018</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>61482</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>43928</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>33431</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>55901</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>80158</t>
+          <t>87916</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64028</t>
+          <t>72980</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97215</t>
+          <t>105389</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>108497</t>
+          <t>115602</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>81297</t>
+          <t>96880</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>128738</t>
+          <t>135092</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>182573</t>
+          <t>198664</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>149687</t>
+          <t>179490</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>207959</t>
+          <t>219737</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>291070</t>
+          <t>314267</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>249435</t>
+          <t>288676</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>323681</t>
+          <t>342630</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>474537</t>
+          <t>504398</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>370117</t>
+          <t>464726</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>529520</t>
+          <t>550000</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>774492</t>
+          <t>777378</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>737271</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>933177</t>
+          <t>820727</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1249029</t>
+          <t>1281776</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1089913</t>
+          <t>1222147</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1415049</t>
+          <t>1344862</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2226854</t>
+          <t>2212086</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2109282</t>
+          <t>2144543</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2485108</t>
+          <t>2272741</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2258371</t>
+          <t>2283381</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2115729</t>
+          <t>2232340</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2514394</t>
+          <t>2333829</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4485225</t>
+          <t>4495468</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4276852</t>
+          <t>4405333</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4811774</t>
+          <t>4580841</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>63,19%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>605771</t>
+          <t>650069</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>472968</t>
+          <t>593978</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>685086</t>
+          <t>707790</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>394430</t>
+          <t>419496</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>320520</t>
+          <t>386087</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>490315</t>
+          <t>462942</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1000201</t>
+          <t>1069565</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>865987</t>
+          <t>997694</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1123129</t>
+          <t>1140332</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
